--- a/Experiment: C1/data/density_analysis_of_the_liquid_detergent.xlsx
+++ b/Experiment: C1/data/density_analysis_of_the_liquid_detergent.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Lab C1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB739856-99A4-4A9E-9849-1C3DAD2569D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A1E5EC-9C27-43EB-A337-019BFD07C176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24C54B25-8088-4F7A-8894-89F8110B386F}"/>
   </bookViews>
@@ -60,14 +60,14 @@
     <t>Mean Mass /g</t>
   </si>
   <si>
-    <t>Std Dev of Mass /g</t>
+    <t>Std Error of Mass /g</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,8 +108,15 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,8 +135,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0DBF0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -209,11 +222,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4472C4"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF4472C4"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF4472C4"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF4472C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -243,6 +271,15 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -903,8 +940,8 @@
       <c r="E3" s="6">
         <v>3.786</v>
       </c>
-      <c r="F3" s="6">
-        <v>1.391</v>
+      <c r="F3" s="11">
+        <v>0.56789000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -923,8 +960,8 @@
       <c r="E4" s="8">
         <v>8.2330000000000005</v>
       </c>
-      <c r="F4" s="8">
-        <v>1.752</v>
+      <c r="F4" s="12">
+        <v>0.71511000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -943,8 +980,8 @@
       <c r="E5" s="6">
         <v>17.920999999999999</v>
       </c>
-      <c r="F5" s="6">
-        <v>2.46</v>
+      <c r="F5" s="13">
+        <v>1.0042899999999999</v>
       </c>
     </row>
   </sheetData>
